--- a/planilhas/DADOS_CLIENTES_CONS.xlsx
+++ b/planilhas/DADOS_CLIENTES_CONS.xlsx
@@ -1,1476 +1,1478 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karol/Documents/Dashboard-Ativuz/planilhas/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17049CE-FFED-7C4A-8C72-942964CF6509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Clientes" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Clientes" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Clientes!$A$1:$Q$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Clientes!$A$1:$Q$1</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="478">
-  <si>
-    <t xml:space="preserve">Cliente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPF Condutor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ano Modelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chassi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endereço</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CEP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nº Motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telefone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contrato de Locação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contrato Comercial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipo de Contrato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Início do Contrato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Término do Contrato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidade do Veículo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">097.034.444-90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG45U5LT080519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VOLKSWAGEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOL 1.0 FLEX 12V 5P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QGW-2B89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TV. SÃO SEBASTIÃO, nº 198, ALECRIM, NATAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE535361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 981787788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1077-1/4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOTORISTA DE APLICATIVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATIVUZ VEÍCULOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.020.944-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG5R13RT050109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLO TRACK 1.0 FLEX 12V 5P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STX-6G05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA SENADOR JESSE PINTO FREIRE 38, LAGOA NOVA/AREA URBANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE937312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 98635-7625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1076-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.205.544-37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG45UXJT141960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOL TRENDLINE 1.0 T.FLEX 12V 5P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QGX-7353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA NÚMERO DEZ, Nº 180-A, REDINHA, NATAL/RN, CEP:59122-145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59073-070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE297532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84 99616-2852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1028-1/8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/07/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">700.139.284-73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG45UXMT107456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGE-5D51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA MIRANTE DO RIO, 21 98 - POTENGI - NATAL/RN 59120-606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59120-606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE602859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 996939545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1010-1/9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">014.010.004-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG45U6MT106935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGE-7G92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AV OLAVO LACERDA MONTENEGRO, 6675 AP 203, PARQUE DAS ÁRVORES, PARNAMIRIM/RN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59056-510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE602667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84 98651-5656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1006-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/08/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.338.594-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG45U5MT005952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QGT-9D76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA PREFEITO GENTIL FERREIRA, 22 - QUINTAS, 59050-050 NATAL/RN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE272295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 987067181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1049-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/10/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.136.017-55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG45U9MT107528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGE-7H03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA EDSON TEIXEIRA DA SILVA, Nº 270, PONTA NEGRA, NATAL, CEP:59090-568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59090-568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE602931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84 99837-3901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1032-1/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.144.684-41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG45UXMT107795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGE-5D71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA PROFESSOR GERSON DUMARESQ Nº 365, CAPIM MACIO CEP: 59082-330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE818939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 994770401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1060-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TERCEIRIZAÇÃO DE FROTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/01/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/01/2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.631.134-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDB45U7LT066973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VOYAGE 1.6 MSI FLEX 8V 4P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QGT-1D67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA ABÍLIO DEODATO, 010 - NOSSA SENHORA DE NAZARÉ, CEP:59062-070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCRAY7720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84)98867-7423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1070-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">480.697.874-49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDB45U5KT135660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QGU-1H54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA PLANICE DO POTENGI, Nº 209, PAJUÇARA, CEP:59123-575, NATAL/RN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59123-575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCRAU1595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 996369127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1022-1/4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">071.198.454-97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDB45U9KT124595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QSE-8E63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA JOAQUIM CALDAS MOREIRA, Nº 151, LAGOA AZUL, NATAL/RN, CEP:59129-780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59129-780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCRAT1699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 981397610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1015-1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAVI HENRIQUE DANTAS DE SOUZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">092.354.354-63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDB45U1LT065429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QGS-6G16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA SANTO CRISTO, Nº 968, PAJUÇARA, NATAL, CEP:59133-304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59133-304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCRAY7001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84 92148-9407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1004-1/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">017.712.914-00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG45U2KT043944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QGN-9356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA ENGENHEIRO JOÃO H ALVES ROCHA, Nº 820 AP-102, PLANALTO, NATAL/RN, CEP:59073-070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE322705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 921520363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1019-1/3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">081.855.524-60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAB45U9LT064192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QGS-5J76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA DOS CAJUEIROS 115 - FT AP-505, NOVA PARNAMIRIM, CEP:59150-600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCRAY5305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 996176525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1064-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GILVAN RODRIGUES MACHADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.762.214-73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93Y5SRZ85MJ355273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRATA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RENAULT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SANDERO LIFE FLEX 1.0 12V 5P MEC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QXL-1E71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA CAMPO DA RIBEIRA, 121 - CAJUPIRANGA, PARNAMIRIM/RN, CEP:59.156-813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE381577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 998016186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1054-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/12/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">069.054.054-00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45U8NT005796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VOYAGE 1.0 FLEX 12V 4P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RMK-2H75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA BOA VISTA, Nº 05, AMARANTE - SÃO GONÇALO DO AMARANTE, CEP:59296-620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59296-620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE609263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 981911956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1024-1/7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.033.332-72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG45U8MT050030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGE-3I66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TV ITINGA, 16, LOT VALE DOURADO, NATAL/RN, CEP:59114-205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59114-205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE397737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84 99639-9401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1017-1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">033.444.532-97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45U4PT034716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZY-6E03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA BARCELONA 370 APTO 05, NOVA PARNAMIRIM, PARNAMIRIM/RN CEP:59284-292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE471326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 991236644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1051-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/11/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.936.764-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45U7PT091086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECZ-8C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA MARIA MARTA MACHADO, 244, NOVA ESPERANÇA, PARNAMIRIM/RN, CEP:59144-318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59144-318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE831159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84 98890-2831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1016-1/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">090.251.774-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45U7PT080055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CINZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EJZ-3D41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA DOS GIRASSOIS, 31 - JARDINS, SÃO GONÇALO DO AMARANTE/RN, CEP:59292-432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE819345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 921482452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1047-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/10/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.201.114-76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45U2PT060313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVE-7G53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END. IRMA VITORIA 155 IGAPO, NATAL/RN, CEP:59106-029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE555819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 987574610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1043-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/09/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.762.454-96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45UXPT092720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXF-1F14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA SANTO AGOSTINHO, N 1011, IGAPÓ, NATAL/RN, CEP 59104-240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59104-240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE833245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 921697458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1029-1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">061.040.714-73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45U0PT034373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EWJ-2I45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA DOUTOR AMARO IENAGA, 290 AP-201, PAJUÇARA, NATAL/RN, CEP:59131-510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE469879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 99263873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1056-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/01/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">086.170.784-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45U2PT077211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECM-1C93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AV MEDELLIN 222 LOT BOA ESPERANÇA, LAGOA AZUL, NATAL/RN 59139-340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE816480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1068-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARCELO BENTO DE ARAUJO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">966.730.874-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45U5NT045320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNC-4J20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA DOS TORORÓS, 335 - ALECRIM, NATAL/RN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE617334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 921505105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1013-1/8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MILENA PORTILHA UGOLINI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720.839.894-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45U4PT003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUC-5C24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA GRANGEMORE 25, BISHOP O DONNEL ROAD, GALWAY, IRLANDA CEP:H91 EK8R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59090-315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE625785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1052-1/3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARRO POR ASSINATURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/11/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">017.778.694-98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45U5PT081673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFF-7I05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA SENADOR JESSE PINTO FREIRE 38 - LAGOA NOVA, NATAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE820863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 991660839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1063-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">035.542.114-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG5R19RT023738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSW-1A28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA CEL COELHO, N, 201 - BOM PASTOR - NATAL RN 59060-240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE907483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 99997-2421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1067-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">009.896.264-74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG45U4MT107453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VOLKSWAGEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGE-7H02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AV AYRTON SENNA, 426 - BL B
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="479">
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>CPF Condutor</t>
+  </si>
+  <si>
+    <t>Ano Modelo</t>
+  </si>
+  <si>
+    <t>Chassi</t>
+  </si>
+  <si>
+    <t>Cor</t>
+  </si>
+  <si>
+    <t>Marca</t>
+  </si>
+  <si>
+    <t>Modelo</t>
+  </si>
+  <si>
+    <t>Placa</t>
+  </si>
+  <si>
+    <t>Endereço</t>
+  </si>
+  <si>
+    <t>CEP</t>
+  </si>
+  <si>
+    <t>Nº Motor</t>
+  </si>
+  <si>
+    <t>Telefone</t>
+  </si>
+  <si>
+    <t>Contrato de Locação</t>
+  </si>
+  <si>
+    <t>Contrato Comercial</t>
+  </si>
+  <si>
+    <t>Tipo de Contrato</t>
+  </si>
+  <si>
+    <t>Início do Contrato</t>
+  </si>
+  <si>
+    <t>Término do Contrato</t>
+  </si>
+  <si>
+    <t>Unidade do Veículo</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>097.034.444-90</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>9BWAG45U5LT080519</t>
+  </si>
+  <si>
+    <t>BRANCA</t>
+  </si>
+  <si>
+    <t>VOLKSWAGEM</t>
+  </si>
+  <si>
+    <t>GOL 1.0 FLEX 12V 5P</t>
+  </si>
+  <si>
+    <t>QGW-2B89</t>
+  </si>
+  <si>
+    <t>TV. SÃO SEBASTIÃO, nº 198, ALECRIM, NATAL</t>
+  </si>
+  <si>
+    <t>CSE535361</t>
+  </si>
+  <si>
+    <t>(84) 98178-7788</t>
+  </si>
+  <si>
+    <t>LOC-1077-1/4</t>
+  </si>
+  <si>
+    <t>CTO-1077</t>
+  </si>
+  <si>
+    <t>MOTORISTA DE APLICATIVO</t>
+  </si>
+  <si>
+    <t>04/05/2026</t>
+  </si>
+  <si>
+    <t>01/06/2026</t>
+  </si>
+  <si>
+    <t>ATIVUZ VEÍCULOS</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>113.020.944-08</t>
+  </si>
+  <si>
+    <t>9BWAG5R13RT050109</t>
+  </si>
+  <si>
+    <t>POLO TRACK 1.0 FLEX 12V 5P</t>
+  </si>
+  <si>
+    <t>STX-6G05</t>
+  </si>
+  <si>
+    <t>RUA SENADOR JESSE PINTO FREIRE 38, LAGOA NOVA/AREA URBANA</t>
+  </si>
+  <si>
+    <t>CSE937312</t>
+  </si>
+  <si>
+    <t>(84) 98635-7625</t>
+  </si>
+  <si>
+    <t>LOC-1076-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1076</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>120.205.544-37</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>9BWAG45UXJT141960</t>
+  </si>
+  <si>
+    <t>GOL TRENDLINE 1.0 T.FLEX 12V 5P</t>
+  </si>
+  <si>
+    <t>QGX-7353</t>
+  </si>
+  <si>
+    <t>RUA NÚMERO DEZ, Nº 180-A, REDINHA, NATAL/RN, CEP:59122-145</t>
+  </si>
+  <si>
+    <t>59073-070</t>
+  </si>
+  <si>
+    <t>CSE297532</t>
+  </si>
+  <si>
+    <t>(84) 99616-2852</t>
+  </si>
+  <si>
+    <t>LOC-1028-1/8</t>
+  </si>
+  <si>
+    <t>CTO-1028</t>
+  </si>
+  <si>
+    <t>23/07/2025</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>700.139.284-73</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>9BWAG45UXMT107456</t>
+  </si>
+  <si>
+    <t>RGE-5D51</t>
+  </si>
+  <si>
+    <t>RUA MIRANTE DO RIO, 21 98 - POTENGI - NATAL/RN 59120-606</t>
+  </si>
+  <si>
+    <t>59120-606</t>
+  </si>
+  <si>
+    <t>CSE602859</t>
+  </si>
+  <si>
+    <t>(84) 99693-9545</t>
+  </si>
+  <si>
+    <t>LOC-1010-1/9</t>
+  </si>
+  <si>
+    <t>CTO-1010</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>014.010.004-01</t>
+  </si>
+  <si>
+    <t>9BWAG45U6MT106935</t>
+  </si>
+  <si>
+    <t>RGE-7G92</t>
+  </si>
+  <si>
+    <t>AV OLAVO LACERDA MONTENEGRO, 6675 AP 203, PARQUE DAS ÁRVORES, PARNAMIRIM/RN</t>
+  </si>
+  <si>
+    <t>59056-510</t>
+  </si>
+  <si>
+    <t>CSE602667</t>
+  </si>
+  <si>
+    <t>(84) 98651-5656</t>
+  </si>
+  <si>
+    <t>LOC-1006-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1006</t>
+  </si>
+  <si>
+    <t>04/08/2025</t>
+  </si>
+  <si>
+    <t>25/05/2026</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>104.338.594-07</t>
+  </si>
+  <si>
+    <t>9BWAG45U5MT005952</t>
+  </si>
+  <si>
+    <t>QGT-9D76</t>
+  </si>
+  <si>
+    <t>RUA PREFEITO GENTIL FERREIRA, 22 - QUINTAS, 59050-050 NATAL/RN</t>
+  </si>
+  <si>
+    <t>CSE272295</t>
+  </si>
+  <si>
+    <t>(84) 98706-7181</t>
+  </si>
+  <si>
+    <t>LOC-1049-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1049</t>
+  </si>
+  <si>
+    <t>28/10/2025</t>
+  </si>
+  <si>
+    <t>11/05/2026</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>122.136.017-55</t>
+  </si>
+  <si>
+    <t>9BWAG45U9MT107528</t>
+  </si>
+  <si>
+    <t>RGE-7H03</t>
+  </si>
+  <si>
+    <t>RUA EDSON TEIXEIRA DA SILVA, Nº 270, PONTA NEGRA, NATAL, CEP:59090-568</t>
+  </si>
+  <si>
+    <t>59090-568</t>
+  </si>
+  <si>
+    <t>CSE602931</t>
+  </si>
+  <si>
+    <t>(84) 99837-3901</t>
+  </si>
+  <si>
+    <t>LOC-1032-1/1</t>
+  </si>
+  <si>
+    <t>CTO-1032</t>
+  </si>
+  <si>
+    <t>22/06/2026</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>100.144.684-41</t>
+  </si>
+  <si>
+    <t>9BWAG45UXMT107795</t>
+  </si>
+  <si>
+    <t>RGE-5D71</t>
+  </si>
+  <si>
+    <t>RUA PROFESSOR GERSON DUMARESQ Nº 365, CAPIM MACIO CEP: 59082-330</t>
+  </si>
+  <si>
+    <t>CSE818939</t>
+  </si>
+  <si>
+    <t>(84) 99477-0401</t>
+  </si>
+  <si>
+    <t>LOC-1060-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1060</t>
+  </si>
+  <si>
+    <t>TERCEIRIZAÇÃO DE FROTA</t>
+  </si>
+  <si>
+    <t>19/01/2026</t>
+  </si>
+  <si>
+    <t>19/01/2027</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>704.631.134-03</t>
+  </si>
+  <si>
+    <t>9BWDB45U7LT066973</t>
+  </si>
+  <si>
+    <t>VOYAGE 1.6 MSI FLEX 8V 4P</t>
+  </si>
+  <si>
+    <t>QGT-1D67</t>
+  </si>
+  <si>
+    <t>RUA ABÍLIO DEODATO, 010 - NOSSA SENHORA DE NAZARÉ, CEP:59062-070</t>
+  </si>
+  <si>
+    <t>CCRAY7720</t>
+  </si>
+  <si>
+    <t>(84) 98867-7423</t>
+  </si>
+  <si>
+    <t>LOC-1070-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1070</t>
+  </si>
+  <si>
+    <t>06/04/2026</t>
+  </si>
+  <si>
+    <t>29/06/2026</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>480.697.874-49</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>9BWDB45U5KT135660</t>
+  </si>
+  <si>
+    <t>QGU-1H54</t>
+  </si>
+  <si>
+    <t>RUA PLANICE DO POTENGI, Nº 209, PAJUÇARA, CEP:59123-575, NATAL/RN</t>
+  </si>
+  <si>
+    <t>59123-575</t>
+  </si>
+  <si>
+    <t>CCRAU1595</t>
+  </si>
+  <si>
+    <t>(84) 99636-9127</t>
+  </si>
+  <si>
+    <t>LOC-1022-1/4</t>
+  </si>
+  <si>
+    <t>CTO-1022</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>071.198.454-97</t>
+  </si>
+  <si>
+    <t>9BWDB45U9KT124595</t>
+  </si>
+  <si>
+    <t>QSE-8E63</t>
+  </si>
+  <si>
+    <t>RUA JOAQUIM CALDAS MOREIRA, Nº 151, LAGOA AZUL, NATAL/RN, CEP:59129-780</t>
+  </si>
+  <si>
+    <t>59129-780</t>
+  </si>
+  <si>
+    <t>CCRAT1699</t>
+  </si>
+  <si>
+    <t>(84) 98139-7610</t>
+  </si>
+  <si>
+    <t>LOC-1015-1/2</t>
+  </si>
+  <si>
+    <t>CTO-1015</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>092.354.354-63</t>
+  </si>
+  <si>
+    <t>9BWDB45U1LT065429</t>
+  </si>
+  <si>
+    <t>QGS-6G16</t>
+  </si>
+  <si>
+    <t>RUA SANTO CRISTO, Nº 968, PAJUÇARA, NATAL, CEP:59133-304</t>
+  </si>
+  <si>
+    <t>59133-304</t>
+  </si>
+  <si>
+    <t>CCRAY7001</t>
+  </si>
+  <si>
+    <t>(84) 92148-9407</t>
+  </si>
+  <si>
+    <t>LOC-1004-1/5</t>
+  </si>
+  <si>
+    <t>CTO-1004</t>
+  </si>
+  <si>
+    <t>15/06/2026</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>017.712.914-00</t>
+  </si>
+  <si>
+    <t>9BWAG45U2KT043944</t>
+  </si>
+  <si>
+    <t>QGN-9356</t>
+  </si>
+  <si>
+    <t>RUA ENGENHEIRO JOÃO H ALVES ROCHA, Nº 820 AP-102, PLANALTO, NATAL/RN, CEP:59073-070</t>
+  </si>
+  <si>
+    <t>CSE322705</t>
+  </si>
+  <si>
+    <t>(84) 92152-0363</t>
+  </si>
+  <si>
+    <t>LOC-1019-1/3</t>
+  </si>
+  <si>
+    <t>CTO-1019</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>081.855.524-60</t>
+  </si>
+  <si>
+    <t>9BWAB45U9LT064192</t>
+  </si>
+  <si>
+    <t>QGS-5J76</t>
+  </si>
+  <si>
+    <t>RUA DOS CAJUEIROS 115 - FT AP-505, NOVA PARNAMIRIM, CEP:59150-600</t>
+  </si>
+  <si>
+    <t>CCRAY5305</t>
+  </si>
+  <si>
+    <t>(84) 99617-6525</t>
+  </si>
+  <si>
+    <t>LOC-1064-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1064</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>705.762.214-73</t>
+  </si>
+  <si>
+    <t>93Y5SRZ85MJ355273</t>
+  </si>
+  <si>
+    <t>PRATA</t>
+  </si>
+  <si>
+    <t>RENAULT</t>
+  </si>
+  <si>
+    <t>SANDERO LIFE FLEX 1.0 12V 5P MEC.</t>
+  </si>
+  <si>
+    <t>QXL-1E71</t>
+  </si>
+  <si>
+    <t>RUA CAMPO DA RIBEIRA, 121 - CAJUPIRANGA, PARNAMIRIM/RN, CEP:59.156-813</t>
+  </si>
+  <si>
+    <t>CSE381577</t>
+  </si>
+  <si>
+    <t>(84) 99801-6186</t>
+  </si>
+  <si>
+    <t>LOC-1054-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1054</t>
+  </si>
+  <si>
+    <t>12/12/2025</t>
+  </si>
+  <si>
+    <t>27/04/2026</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>069.054.054-00</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>9BWDG45U8NT005796</t>
+  </si>
+  <si>
+    <t>VOYAGE 1.0 FLEX 12V 4P</t>
+  </si>
+  <si>
+    <t>RMK-2H75</t>
+  </si>
+  <si>
+    <t>RUA BOA VISTA, Nº 05, AMARANTE - SÃO GONÇALO DO AMARANTE, CEP:59296-620</t>
+  </si>
+  <si>
+    <t>59296-620</t>
+  </si>
+  <si>
+    <t>CSE609263</t>
+  </si>
+  <si>
+    <t>(84) 98191-1956</t>
+  </si>
+  <si>
+    <t>LOC-1024-1/7</t>
+  </si>
+  <si>
+    <t>CTO-1024</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>415.033.332-72</t>
+  </si>
+  <si>
+    <t>9BWAG45U8MT050030</t>
+  </si>
+  <si>
+    <t>RGE-3I66</t>
+  </si>
+  <si>
+    <t>TV ITINGA, 16, LOT VALE DOURADO, NATAL/RN, CEP:59114-205</t>
+  </si>
+  <si>
+    <t>59114-205</t>
+  </si>
+  <si>
+    <t>CSE397737</t>
+  </si>
+  <si>
+    <t>(84) 99639-9401</t>
+  </si>
+  <si>
+    <t>LOC-1017-1/2</t>
+  </si>
+  <si>
+    <t>CTO-1017</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>033.444.532-97</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>9BWDG45U4PT034716</t>
+  </si>
+  <si>
+    <t>EZY-6E03</t>
+  </si>
+  <si>
+    <t>RUA BARCELONA 370 APTO 05, NOVA PARNAMIRIM, PARNAMIRIM/RN CEP:59284-292</t>
+  </si>
+  <si>
+    <t>CSE471326</t>
+  </si>
+  <si>
+    <t>(84) 99123-6644</t>
+  </si>
+  <si>
+    <t>LOC-1051-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1051</t>
+  </si>
+  <si>
+    <t>19/11/2025</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>117.936.764-29</t>
+  </si>
+  <si>
+    <t>9BWDG45U7PT091086</t>
+  </si>
+  <si>
+    <t>ECZ-8C02</t>
+  </si>
+  <si>
+    <t>RUA MARIA MARTA MACHADO, 244, NOVA ESPERANÇA, PARNAMIRIM/RN, CEP:59144-318</t>
+  </si>
+  <si>
+    <t>59144-318</t>
+  </si>
+  <si>
+    <t>CSE831159</t>
+  </si>
+  <si>
+    <t>(84) 98890-2831</t>
+  </si>
+  <si>
+    <t>LOC-1016-1/5</t>
+  </si>
+  <si>
+    <t>CTO-1016</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>090.251.774-09</t>
+  </si>
+  <si>
+    <t>9BWDG45U7PT080055</t>
+  </si>
+  <si>
+    <t>CINZA</t>
+  </si>
+  <si>
+    <t>EJZ-3D41</t>
+  </si>
+  <si>
+    <t>RUA DOS GIRASSOIS, 31 - JARDINS, SÃO GONÇALO DO AMARANTE/RN, CEP:59292-432</t>
+  </si>
+  <si>
+    <t>CSE819345</t>
+  </si>
+  <si>
+    <t>(84) 92148-2452</t>
+  </si>
+  <si>
+    <t>LOC-1047-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1047</t>
+  </si>
+  <si>
+    <t>27/10/2025</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>704.201.114-76</t>
+  </si>
+  <si>
+    <t>9BWDG45U2PT060313</t>
+  </si>
+  <si>
+    <t>EVE-7G53</t>
+  </si>
+  <si>
+    <t>END. IRMA VITORIA 155 IGAPO, NATAL/RN, CEP:59106-029</t>
+  </si>
+  <si>
+    <t>CSE555819</t>
+  </si>
+  <si>
+    <t>(84) 98757-4610</t>
+  </si>
+  <si>
+    <t>LOC-1043-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1043</t>
+  </si>
+  <si>
+    <t>15/09/2025</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>705.762.454-96</t>
+  </si>
+  <si>
+    <t>9BWDG45UXPT092720</t>
+  </si>
+  <si>
+    <t>EXF-1F14</t>
+  </si>
+  <si>
+    <t>RUA SANTO AGOSTINHO, N 1011, IGAPÓ, NATAL/RN, CEP 59104-240</t>
+  </si>
+  <si>
+    <t>59104-240</t>
+  </si>
+  <si>
+    <t>CSE833245</t>
+  </si>
+  <si>
+    <t>(84) 92169-7458</t>
+  </si>
+  <si>
+    <t>LOC-1029-1/2</t>
+  </si>
+  <si>
+    <t>CTO-1029</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>061.040.714-73</t>
+  </si>
+  <si>
+    <t>9BWDG45U0PT034373</t>
+  </si>
+  <si>
+    <t>EWJ-2I45</t>
+  </si>
+  <si>
+    <t>RUA DOUTOR AMARO IENAGA, 290 AP-201, PAJUÇARA, NATAL/RN, CEP:59131-510</t>
+  </si>
+  <si>
+    <t>CSE469879</t>
+  </si>
+  <si>
+    <t>(84) 99926-3873</t>
+  </si>
+  <si>
+    <t>LOC-1056-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1056</t>
+  </si>
+  <si>
+    <t>09/01/2026</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>086.170.784-21</t>
+  </si>
+  <si>
+    <t>9BWDG45U2PT077211</t>
+  </si>
+  <si>
+    <t>ECM-1C93</t>
+  </si>
+  <si>
+    <t>AV MEDELLIN 222 LOT BOA ESPERANÇA, LAGOA AZUL, NATAL/RN 59139-340</t>
+  </si>
+  <si>
+    <t>CSE816480</t>
+  </si>
+  <si>
+    <t>(84) 98828-7320</t>
+  </si>
+  <si>
+    <t>LOC-1068-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1068</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>08/06/2026</t>
+  </si>
+  <si>
+    <t>MARCELO BENTO DE ARAUJO</t>
+  </si>
+  <si>
+    <t>966.730.874-04</t>
+  </si>
+  <si>
+    <t>9BWDG45U5NT045320</t>
+  </si>
+  <si>
+    <t>RNC-4J20</t>
+  </si>
+  <si>
+    <t>RUA DOS TORORÓS, 335 - ALECRIM, NATAL/RN</t>
+  </si>
+  <si>
+    <t>CSE617334</t>
+  </si>
+  <si>
+    <t>(84) 92150-5105</t>
+  </si>
+  <si>
+    <t>LOC-1013-1/8</t>
+  </si>
+  <si>
+    <t>CTO-1013</t>
+  </si>
+  <si>
+    <t>MILENA PORTILHA UGOLINI</t>
+  </si>
+  <si>
+    <t>720.839.894-14</t>
+  </si>
+  <si>
+    <t>9BWDG45U4PT003479</t>
+  </si>
+  <si>
+    <t>RUC-5C24</t>
+  </si>
+  <si>
+    <t>RUA GRANGEMORE 25, BISHOP O DONNEL ROAD, GALWAY, IRLANDA CEP:H91 EK8R</t>
+  </si>
+  <si>
+    <t>59090-315</t>
+  </si>
+  <si>
+    <t>CSE625785</t>
+  </si>
+  <si>
+    <t>LOC-1052-1/3</t>
+  </si>
+  <si>
+    <t>CTO-1052</t>
+  </si>
+  <si>
+    <t>CARRO POR ASSINATURA</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
+    <t>26/05/2026</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>017.778.694-98</t>
+  </si>
+  <si>
+    <t>9BWDG45U5PT081673</t>
+  </si>
+  <si>
+    <t>EFF-7I05</t>
+  </si>
+  <si>
+    <t>RUA SENADOR JESSE PINTO FREIRE 38 - LAGOA NOVA, NATAL</t>
+  </si>
+  <si>
+    <t>CSE820863</t>
+  </si>
+  <si>
+    <t>(84) 99166-0839</t>
+  </si>
+  <si>
+    <t>LOC-1063-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1063</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>035.542.114-35</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>9BWAG5R19RT023738</t>
+  </si>
+  <si>
+    <t>SSW-1A28</t>
+  </si>
+  <si>
+    <t>RUA CEL COELHO, N, 201 - BOM PASTOR - NATAL RN 59060-240</t>
+  </si>
+  <si>
+    <t>CSE907483</t>
+  </si>
+  <si>
+    <t>(84) 99997-2421</t>
+  </si>
+  <si>
+    <t>LOC-1067-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1067</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>009.896.264-74</t>
+  </si>
+  <si>
+    <t>9BWAG45U4MT107453</t>
+  </si>
+  <si>
+    <t>VOLKSWAGEN</t>
+  </si>
+  <si>
+    <t>RGE-7H02</t>
+  </si>
+  <si>
+    <t>AV AYRTON SENNA, 426 - BL B
 APTO 203</t>
   </si>
   <si>
-    <t xml:space="preserve">59084-100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE602857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1071-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEW CHARGER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.346.152/0001-41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG45U4MT005800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QGT-9D86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA ALEXANDRIA, nº 1730, LAGOA NOVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59054-780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1073-1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.802.049/0001-63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA MANOEL PATRICIO DE MEDEIROS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 999250268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">725.770.104-00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA MANOEL FRANCISCO RIBEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 988605262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEGCOMP TECNOLOGIA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.153.812/0001-54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG45U9PT049067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EGX-2E31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AV XAVIER DA SILVEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59056-530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 30133030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1038-1/24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/10/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.093.374-41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45U3PT091098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END-0I15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA SENADOR NABUCO DE ARAUJO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59131-070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 987180189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1011-1/9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9C2KC2500RR115224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERMELHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HONDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CG 160 START</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RQI-7A69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1038-3/24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9C2KC2500RR115213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RQI-7A89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1038-4/24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9C2KD0810RR165173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NXR 160 BROS ESDD FLEXONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RQJ-7H29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1038-2/24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">790.887.914-49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45U1PT092539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMQ-6C26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AV PRAIA DE TIBAU 2262A PONTA NEGRA, NATAL/RN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59094-500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 81731538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1018-1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">009.554.944-78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWDG45U1PT010258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIY-6G96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA VALTER FERNANDES, 1853, CAPIM MACIO - NATAL / RN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59082-090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 99212-8471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1023-1/13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">059.640.564-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92VCE4CC9VK025626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BYD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOLPHIN MINI (ELÉTRICO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSW-3H63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AV BRIGADEIRO SOUTO 171 BOA
+    <t>59084-100</t>
+  </si>
+  <si>
+    <t>CSE602857</t>
+  </si>
+  <si>
+    <t>LOC-1071-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1071</t>
+  </si>
+  <si>
+    <t>13/04/2026</t>
+  </si>
+  <si>
+    <t>06/07/2026</t>
+  </si>
+  <si>
+    <t>NEW CHARGER</t>
+  </si>
+  <si>
+    <t>46.346.152/0001-41</t>
+  </si>
+  <si>
+    <t>9BWAG45U4MT005800</t>
+  </si>
+  <si>
+    <t>QGT-9D86</t>
+  </si>
+  <si>
+    <t>RUA ALEXANDRIA, nº 1730, LAGOA NOVA</t>
+  </si>
+  <si>
+    <t>59054-780</t>
+  </si>
+  <si>
+    <t>LOC-1073-1/2</t>
+  </si>
+  <si>
+    <t>CTO-1073</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>07/06/2026</t>
+  </si>
+  <si>
+    <t>23.802.049/0001-63</t>
+  </si>
+  <si>
+    <t>RUA MANOEL PATRICIO DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>(84) 99925-0268</t>
+  </si>
+  <si>
+    <t>725.770.104-00</t>
+  </si>
+  <si>
+    <t>RUA MANOEL FRANCISCO RIBEIRO</t>
+  </si>
+  <si>
+    <t>(84) 98860-5262</t>
+  </si>
+  <si>
+    <t>SEGCOMP TECNOLOGIA LTDA</t>
+  </si>
+  <si>
+    <t>41.153.812/0001-54</t>
+  </si>
+  <si>
+    <t>9BWAG45U9PT049067</t>
+  </si>
+  <si>
+    <t>EGX-2E31</t>
+  </si>
+  <si>
+    <t>AV XAVIER DA SILVEIRA</t>
+  </si>
+  <si>
+    <t>59056-530</t>
+  </si>
+  <si>
+    <t>(84) 93013-3030</t>
+  </si>
+  <si>
+    <t>LOC-1038-1/24</t>
+  </si>
+  <si>
+    <t>CTO-1038</t>
+  </si>
+  <si>
+    <t>25/10/2024</t>
+  </si>
+  <si>
+    <t>25/10/2026</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>101.093.374-41</t>
+  </si>
+  <si>
+    <t>9BWDG45U3PT091098</t>
+  </si>
+  <si>
+    <t>END-0I15</t>
+  </si>
+  <si>
+    <t>RUA SENADOR NABUCO DE ARAUJO</t>
+  </si>
+  <si>
+    <t>59131-070</t>
+  </si>
+  <si>
+    <t>(84) 98718-0189</t>
+  </si>
+  <si>
+    <t>LOC-1011-1/9</t>
+  </si>
+  <si>
+    <t>CTO-1011</t>
+  </si>
+  <si>
+    <t>9C2KC2500RR115224</t>
+  </si>
+  <si>
+    <t>VERMELHA</t>
+  </si>
+  <si>
+    <t>HONDA</t>
+  </si>
+  <si>
+    <t>CG 160 START</t>
+  </si>
+  <si>
+    <t>RQI-7A69</t>
+  </si>
+  <si>
+    <t>LOC-1038-3/24</t>
+  </si>
+  <si>
+    <t>9C2KC2500RR115213</t>
+  </si>
+  <si>
+    <t>RQI-7A89</t>
+  </si>
+  <si>
+    <t>LOC-1038-4/24</t>
+  </si>
+  <si>
+    <t>9C2KD0810RR165173</t>
+  </si>
+  <si>
+    <t>PRETA</t>
+  </si>
+  <si>
+    <t>NXR 160 BROS ESDD FLEXONE</t>
+  </si>
+  <si>
+    <t>RQJ-7H29</t>
+  </si>
+  <si>
+    <t>LOC-1038-2/24</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>790.887.914-49</t>
+  </si>
+  <si>
+    <t>9BWDG45U1PT092539</t>
+  </si>
+  <si>
+    <t>EMQ-6C26</t>
+  </si>
+  <si>
+    <t>AV PRAIA DE TIBAU 2262A PONTA NEGRA, NATAL/RN</t>
+  </si>
+  <si>
+    <t>59094-500</t>
+  </si>
+  <si>
+    <t>(84) 98173-1538</t>
+  </si>
+  <si>
+    <t>LOC-1018-1/2</t>
+  </si>
+  <si>
+    <t>CTO-1018</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>009.554.944-78</t>
+  </si>
+  <si>
+    <t>9BWDG45U1PT010258</t>
+  </si>
+  <si>
+    <t>GIY-6G96</t>
+  </si>
+  <si>
+    <t>RUA VALTER FERNANDES, 1853, CAPIM MACIO - NATAL / RN</t>
+  </si>
+  <si>
+    <t>59082-090</t>
+  </si>
+  <si>
+    <t>(84) 99212-8471</t>
+  </si>
+  <si>
+    <t>LOC-1023-1/13</t>
+  </si>
+  <si>
+    <t>CTO-1023</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>059.640.564-23</t>
+  </si>
+  <si>
+    <t>2027</t>
+  </si>
+  <si>
+    <t>92VCE4CC9VK025626</t>
+  </si>
+  <si>
+    <t>BYD</t>
+  </si>
+  <si>
+    <t>DOLPHIN MINI (ELÉTRICO)</t>
+  </si>
+  <si>
+    <t>TSW-3H63</t>
+  </si>
+  <si>
+    <t>AV BRIGADEIRO SOUTO 171 BOA
 ESPERANCA/AREA URBANA</t>
   </si>
   <si>
-    <t xml:space="preserve">59140-590</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7R5092111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 98846-9029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1075-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADRIANO TEOTONIO DA SILVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">031.396.964-77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92VCE4CC1VK025636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSW-3I03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVENIDA MARIA LACERDA MONTENEGRO Nº 850, BLOCO 07, NOVA PARNAMIRIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59152-600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4H5077275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84)9 2001-7417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1074-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.001.424-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAB45U2JT067951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOL (NOVO) 1.6 MI TOTAL FLEX 8V 4P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QGO-2H58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA ALVORADA 707 CS-A IGAPO/AREA URBANA NATAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59104-210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCRX62931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84)9 9427-7882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1078-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">068.435.674-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92VCE4CC0VK025644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSW-3H91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA SÃO RAFAEL, 192 -
+    <t>59140-590</t>
+  </si>
+  <si>
+    <t>7R5092111</t>
+  </si>
+  <si>
+    <t>(84) 98846-9029</t>
+  </si>
+  <si>
+    <t>LOC-1075-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1075</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
+  </si>
+  <si>
+    <t>20/07/2026</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>ADRIANO TEOTONIO DA SILVA</t>
+  </si>
+  <si>
+    <t>031.396.964-77</t>
+  </si>
+  <si>
+    <t>92VCE4CC1VK025636</t>
+  </si>
+  <si>
+    <t>TSW-3I03</t>
+  </si>
+  <si>
+    <t>AVENIDA MARIA LACERDA MONTENEGRO Nº 850, BLOCO 07, NOVA PARNAMIRIM</t>
+  </si>
+  <si>
+    <t>59152-600</t>
+  </si>
+  <si>
+    <t>4H5077275</t>
+  </si>
+  <si>
+    <t>(84) 92001-7417</t>
+  </si>
+  <si>
+    <t>LOC-1074-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1074</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>27/07/2026</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>105.001.424-32</t>
+  </si>
+  <si>
+    <t>9BWAB45U2JT067951</t>
+  </si>
+  <si>
+    <t>GOL (NOVO) 1.6 MI TOTAL FLEX 8V 4P</t>
+  </si>
+  <si>
+    <t>QGO-2H58</t>
+  </si>
+  <si>
+    <t>RUA ALVORADA 707 CS-A IGAPO/AREA URBANA NATAL</t>
+  </si>
+  <si>
+    <t>59104-210</t>
+  </si>
+  <si>
+    <t>CCRX62931</t>
+  </si>
+  <si>
+    <t>(84) 99427-7882</t>
+  </si>
+  <si>
+    <t>LOC-1078-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1078</t>
+  </si>
+  <si>
+    <t>08/05/2026</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>068.435.674-01</t>
+  </si>
+  <si>
+    <t>92VCE4CC0VK025644</t>
+  </si>
+  <si>
+    <t>TSW-3H91</t>
+  </si>
+  <si>
+    <t>RUA SÃO RAFAEL, 192 -
 GRUTAS/ EXTREMOZ</t>
   </si>
   <si>
-    <t xml:space="preserve">59575-000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7R5090229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 99819-7194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1079-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUCA ZOLI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">014.009.964-65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9BWAG45U9LT036412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QGT-6I05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA FLOR DA AURORA, N 85 AP 3, PONTA NEGRA, NATAL, RN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59090-725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(84) 99991-6280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1081-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.421.724-70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92VCE4CC0VK025501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSW-3I66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA PADRE RAIMUNDO BRASIL, 1051, NOVA DESCOBERTA, NATAL, RN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59075-100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7R5092295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(12) 99132-3178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC-1080-1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTO-1080</t>
+    <t>59575-000</t>
+  </si>
+  <si>
+    <t>7R5090229</t>
+  </si>
+  <si>
+    <t>(84) 99819-7194</t>
+  </si>
+  <si>
+    <t>LOC-1079-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1079</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>014.009.964-65</t>
+  </si>
+  <si>
+    <t>9BWAG45U9LT036412</t>
+  </si>
+  <si>
+    <t>QGT-6I05</t>
+  </si>
+  <si>
+    <t>RUA FLOR DA AURORA, N 85 AP 3, PONTA NEGRA, NATAL, RN</t>
+  </si>
+  <si>
+    <t>59090-725</t>
+  </si>
+  <si>
+    <t>(84) 99991-6280</t>
+  </si>
+  <si>
+    <t>LOC-1081-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1081</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>124.421.724-70</t>
+  </si>
+  <si>
+    <t>92VCE4CC0VK025501</t>
+  </si>
+  <si>
+    <t>TSW-3I66</t>
+  </si>
+  <si>
+    <t>RUA PADRE RAIMUNDO BRASIL, 1051, NOVA DESCOBERTA, NATAL, RN</t>
+  </si>
+  <si>
+    <t>59075-100</t>
+  </si>
+  <si>
+    <t>7R5092295</t>
+  </si>
+  <si>
+    <t>(12) 99132-3178</t>
+  </si>
+  <si>
+    <t>LOC-1080-1/12</t>
+  </si>
+  <si>
+    <t>CTO-1080</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1479,33 +1481,16 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1548,14 +1533,14 @@
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBDD7EE"/>
       </left>
@@ -1570,7 +1555,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBDD7EE"/>
       </left>
@@ -1582,107 +1567,72 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F3864"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1741,17 +1691,29 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1793,12 +1755,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1827,7 +1789,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1848,7 +1810,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1899,7 +1861,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1917,49 +1879,48 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R46"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="22"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="10" style="14" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="45" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="16" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -2008,15 +1969,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>20</v>
+      <c r="C2" s="13">
+        <v>2020</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>21</v>
@@ -2062,15 +2023,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>20</v>
+      <c r="C3" s="16">
+        <v>2020</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>37</v>
@@ -2106,25 +2067,25 @@
       <c r="O3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="P3" s="4">
         <v>46152</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="Q3" s="4">
         <v>46237</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>48</v>
+      <c r="C4" s="15">
+        <v>2018</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>49</v>
@@ -2172,15 +2133,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>61</v>
+      <c r="C5" s="18">
+        <v>2021</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>62</v>
@@ -2228,15 +2189,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>61</v>
+      <c r="C6" s="19">
+        <v>2021</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>72</v>
@@ -2284,15 +2245,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
+      <c r="C7" s="18">
+        <v>2021</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>84</v>
@@ -2338,15 +2299,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>61</v>
+      <c r="C8" s="19">
+        <v>2021</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>95</v>
@@ -2394,15 +2355,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>104</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>61</v>
+      <c r="C9" s="18">
+        <v>2021</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>106</v>
@@ -2448,15 +2409,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>116</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>20</v>
+      <c r="C10" s="18">
+        <v>2020</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>118</v>
@@ -2502,15 +2463,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>130</v>
+      <c r="C11" s="19">
+        <v>2019</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>131</v>
@@ -2558,15 +2519,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>139</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>130</v>
+      <c r="C12" s="18">
+        <v>2019</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>141</v>
@@ -2614,15 +2575,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>20</v>
+      <c r="C13" s="19">
+        <v>2020</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>151</v>
@@ -2670,14 +2631,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>160</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="18" t="s">
         <v>130</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -2726,14 +2687,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>169</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="19" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -2780,14 +2741,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>179</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="18" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -2834,14 +2795,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>193</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="19" t="s">
         <v>195</v>
       </c>
       <c r="D17" s="2" t="s">
@@ -2890,14 +2851,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="18" t="s">
         <v>61</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -2946,14 +2907,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>215</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="19" t="s">
         <v>217</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -3000,14 +2961,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>226</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="18" t="s">
         <v>217</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -3056,14 +3017,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>236</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="19" t="s">
         <v>217</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -3110,14 +3071,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>247</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="18" t="s">
         <v>217</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -3164,14 +3125,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>257</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="19" t="s">
         <v>217</v>
       </c>
       <c r="D23" s="2" t="s">
@@ -3220,14 +3181,14 @@
         <v>267</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>268</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="18" t="s">
         <v>217</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -3274,14 +3235,14 @@
         <v>267</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>278</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="19" t="s">
         <v>217</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -3306,38 +3267,40 @@
       <c r="K25" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="L25" s="2"/>
+      <c r="L25" s="2" t="s">
+        <v>284</v>
+      </c>
       <c r="M25" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="R25" s="2" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C26" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C26" s="18" t="s">
         <v>195</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>182</v>
@@ -3349,25 +3312,25 @@
         <v>197</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>134</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>31</v>
@@ -3382,18 +3345,18 @@
         <v>267</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C27" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>217</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>22</v>
@@ -3405,49 +3368,49 @@
         <v>197</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C28" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C28" s="18" t="s">
         <v>217</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>22</v>
@@ -3459,29 +3422,29 @@
         <v>197</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>81</v>
@@ -3490,18 +3453,18 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C29" s="2" t="s">
         <v>321</v>
       </c>
+      <c r="C29" s="19" t="s">
+        <v>322</v>
+      </c>
       <c r="D29" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>22</v>
@@ -3513,151 +3476,153 @@
         <v>38</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="R29" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C30" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>61</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="L30" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>327</v>
+      </c>
       <c r="M30" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="R30" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C31" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C31" s="18" t="s">
         <v>61</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O31" s="3" t="s">
         <v>113</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="R31" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C32" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C32" s="19" t="s">
         <v>61</v>
       </c>
       <c r="D32" s="2" t="s">
@@ -3667,7 +3632,7 @@
         <v>22</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>24</v>
@@ -3676,12 +3641,12 @@
         <v>107</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>111</v>
@@ -3702,14 +3667,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>179</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C33" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C33" s="18" t="s">
         <v>61</v>
       </c>
       <c r="D33" s="3" t="s">
@@ -3728,12 +3693,12 @@
         <v>185</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>189</v>
@@ -3754,100 +3719,100 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C34" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C34" s="19" t="s">
         <v>217</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>182</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>113</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R34" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C35" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C35" s="18" t="s">
         <v>217</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>197</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>31</v>
@@ -3862,208 +3827,208 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>321</v>
+        <v>359</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>113</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R36" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>321</v>
+        <v>359</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>322</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O37" s="3" t="s">
         <v>113</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R37" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>321</v>
+        <v>359</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>113</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R38" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="C39" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C39" s="18" t="s">
         <v>217</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>239</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>197</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O39" s="3" t="s">
         <v>31</v>
@@ -4078,48 +4043,48 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C40" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C40" s="19" t="s">
         <v>217</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>197</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>109</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>31</v>
@@ -4134,351 +4099,345 @@
         <v>267</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="C41" s="3" t="s">
         <v>411</v>
       </c>
+      <c r="C41" s="18" t="s">
+        <v>412</v>
+      </c>
       <c r="D41" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>411</v>
+        <v>427</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>412</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>31</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="C43" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C43" s="18" t="s">
         <v>48</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="44" s="9" customFormat="true" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="C44" s="9" t="n">
+        <v>451</v>
+      </c>
+      <c r="C44" s="17">
         <v>2027</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P44" s="11" t="n">
+      <c r="P44" s="11">
         <v>46154</v>
       </c>
-      <c r="Q44" s="11" t="n">
+      <c r="Q44" s="11">
         <v>46246</v>
       </c>
       <c r="R44" s="9" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="45" s="9" customFormat="true" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="C45" s="9" t="n">
+        <v>461</v>
+      </c>
+      <c r="C45" s="17">
         <v>2020</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>24</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K45" s="9" t="s">
         <v>187</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P45" s="11" t="n">
+      <c r="P45" s="11">
         <v>46157</v>
       </c>
-      <c r="Q45" s="11" t="n">
+      <c r="Q45" s="11">
         <v>46249</v>
       </c>
       <c r="R45" s="9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="46" s="9" customFormat="true" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="C46" s="9" t="n">
+        <v>470</v>
+      </c>
+      <c r="C46" s="17">
         <v>2027</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P46" s="11" t="n">
+      <c r="P46" s="11">
         <v>46158</v>
       </c>
-      <c r="Q46" s="11" t="n">
+      <c r="Q46" s="11">
         <v>46250</v>
       </c>
       <c r="R46" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:Q1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>